--- a/prix/sikkens.xlsx
+++ b/prix/sikkens.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1821C4-3DAD-45BB-A9D8-47364DECF615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48408B35-7C38-4082-AC87-0FEFF6E940E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1402,7 +1402,7 @@
         <v>30</v>
       </c>
       <c r="F26" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1578,7 +1578,7 @@
         <v>39</v>
       </c>
       <c r="F35" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/sikkens.xlsx
+++ b/prix/sikkens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48408B35-7C38-4082-AC87-0FEFF6E940E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5CFF86-1BB5-4CB3-BE1F-3E6CC0713FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1242,7 +1242,7 @@
         <v>22</v>
       </c>
       <c r="F18" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="10">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1402,7 +1402,7 @@
         <v>30</v>
       </c>
       <c r="F26" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1698,7 +1698,7 @@
         <v>45</v>
       </c>
       <c r="F41" s="10">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/sikkens.xlsx
+++ b/prix/sikkens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5CFF86-1BB5-4CB3-BE1F-3E6CC0713FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25923A0-A324-485F-B0DC-2EC07CCC39C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -532,10 +532,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -915,14 +915,14 @@
       <c r="C2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>69.350000000000009</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="10">
-        <v>2</v>
+      <c r="F2" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -935,14 +935,14 @@
       <c r="C3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="10">
-        <v>4</v>
+      <c r="F3" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -955,13 +955,13 @@
       <c r="C4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <v>1</v>
       </c>
     </row>
@@ -975,13 +975,13 @@
       <c r="C5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>0</v>
       </c>
     </row>
@@ -995,13 +995,13 @@
       <c r="C6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1015,13 +1015,13 @@
       <c r="C7" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1035,13 +1035,13 @@
       <c r="C8" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1055,13 +1055,13 @@
       <c r="C9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>64.349999999999994</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1075,13 +1075,13 @@
       <c r="C10" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1095,13 +1095,13 @@
       <c r="C11" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>4</v>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
       <c r="C12" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
       <c r="C13" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1155,13 +1155,13 @@
       <c r="C14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1175,13 +1175,13 @@
       <c r="C15" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1195,13 +1195,13 @@
       <c r="C16" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1215,13 +1215,13 @@
       <c r="C17" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>143.92000000000002</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1235,14 +1235,14 @@
       <c r="C18" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>49.95</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="10">
-        <v>3</v>
+      <c r="F18" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1255,13 +1255,13 @@
       <c r="C19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>49.95</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="11">
         <v>-1</v>
       </c>
     </row>
@@ -1275,13 +1275,13 @@
       <c r="C20" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <v>49.95</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1295,13 +1295,13 @@
       <c r="C21" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>49.95</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1315,13 +1315,13 @@
       <c r="C22" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <v>49.95</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1335,13 +1335,13 @@
       <c r="C23" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>49.95</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1355,13 +1355,13 @@
       <c r="C24" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <v>49.95</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1375,13 +1375,13 @@
       <c r="C25" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>49.95</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1395,14 +1395,14 @@
       <c r="C26" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>113.5</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="10">
-        <v>1</v>
+      <c r="F26" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1415,13 +1415,13 @@
       <c r="C27" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>113.5</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1435,13 +1435,13 @@
       <c r="C28" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <v>113.5</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1455,13 +1455,13 @@
       <c r="C29" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>113.5</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1475,13 +1475,13 @@
       <c r="C30" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <v>113.5</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1495,13 +1495,13 @@
       <c r="C31" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <v>113.5</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1515,13 +1515,13 @@
       <c r="C32" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <v>113.5</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1535,13 +1535,13 @@
       <c r="C33" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>113.5</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1551,13 +1551,13 @@
         <v>84</v>
       </c>
       <c r="C34" s="5"/>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <v>2.5</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1571,14 +1571,14 @@
       <c r="C35" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>64.5</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="10">
-        <v>4</v>
+      <c r="F35" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1591,14 +1591,14 @@
       <c r="C36" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <v>64.5</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="10">
-        <v>4</v>
+      <c r="F36" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1611,13 +1611,13 @@
       <c r="C37" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>64.5</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1631,13 +1631,13 @@
       <c r="C38" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <v>64.5</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1651,13 +1651,13 @@
       <c r="C39" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>64.5</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1671,13 +1671,13 @@
       <c r="C40" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <v>64.5</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1691,13 +1691,13 @@
       <c r="C41" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <v>64.5</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="11">
         <v>-1</v>
       </c>
     </row>
@@ -1711,13 +1711,13 @@
       <c r="C42" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <v>64.5</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1731,13 +1731,13 @@
       <c r="C43" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>146.6</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1751,14 +1751,14 @@
       <c r="C44" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <v>146.6</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="10">
-        <v>2</v>
+      <c r="F44" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1771,13 +1771,13 @@
       <c r="C45" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>146.6</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1791,13 +1791,13 @@
       <c r="C46" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <v>146.6</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1811,13 +1811,13 @@
       <c r="C47" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>146.6</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="11">
         <v>0</v>
       </c>
     </row>

--- a/prix/sikkens.xlsx
+++ b/prix/sikkens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25923A0-A324-485F-B0DC-2EC07CCC39C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F50D793-4B91-4A07-92AC-1E43A3AB95F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -936,13 +936,13 @@
         <v>98</v>
       </c>
       <c r="D3" s="10">
-        <v>64.349999999999994</v>
+        <v>71.100000000000009</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1256,13 +1256,13 @@
         <v>115</v>
       </c>
       <c r="D19" s="10">
-        <v>49.95</v>
+        <v>51.18</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1402,7 +1402,7 @@
         <v>30</v>
       </c>
       <c r="F26" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1416,13 +1416,13 @@
         <v>123</v>
       </c>
       <c r="D27" s="10">
-        <v>113.5</v>
+        <v>116.33</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F27" s="11">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1598,7 +1598,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1738,7 +1738,7 @@
         <v>47</v>
       </c>
       <c r="F43" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1758,7 +1758,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/sikkens.xlsx
+++ b/prix/sikkens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F50D793-4B91-4A07-92AC-1E43A3AB95F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39FD94C-1A15-465E-A9BB-8DB38531A783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -916,13 +916,13 @@
         <v>99</v>
       </c>
       <c r="D2" s="10">
-        <v>69.350000000000009</v>
+        <v>71.100000000000009</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="11">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -956,13 +956,13 @@
         <v>100</v>
       </c>
       <c r="D4" s="10">
-        <v>64.349999999999994</v>
+        <v>71.100000000000009</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="F5" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1242,7 +1242,7 @@
         <v>22</v>
       </c>
       <c r="F18" s="11">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1276,13 +1276,13 @@
         <v>116</v>
       </c>
       <c r="D20" s="10">
-        <v>49.95</v>
+        <v>51.2</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1592,13 +1592,13 @@
         <v>98</v>
       </c>
       <c r="D36" s="10">
-        <v>64.5</v>
+        <v>66</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>40</v>
       </c>
       <c r="F36" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1732,7 +1732,7 @@
         <v>130</v>
       </c>
       <c r="D43" s="10">
-        <v>146.6</v>
+        <v>150.25</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>47</v>
